--- a/output/pdf_financials_xlsx/CCDS.xlsx
+++ b/output/pdf_financials_xlsx/CCDS.xlsx
@@ -721,10 +721,10 @@
         <v>-0.14291</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.084537</v>
+        <v>-0.084537</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.177915</v>
+        <v>-1.177915</v>
       </c>
     </row>
     <row r="17">
@@ -813,10 +813,10 @@
         <v>-0.14291</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.084537</v>
+        <v>-0.084537</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.177915</v>
+        <v>-1.177915</v>
       </c>
     </row>
     <row r="21">
@@ -870,10 +870,10 @@
         <v>-0.14291</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.084537</v>
+        <v>-0.084537</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.177915</v>
+        <v>-1.177915</v>
       </c>
     </row>
     <row r="24">
@@ -960,10 +960,10 @@
         <v>-0.14291</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.084537</v>
+        <v>-0.084537</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.177915</v>
+        <v>-1.177915</v>
       </c>
     </row>
     <row r="28">
@@ -998,10 +998,10 @@
         <v>-0.14291</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.276749</v>
+        <v>0.107675</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.423291</v>
+        <v>-0.932539</v>
       </c>
     </row>
     <row r="30">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>76.71128456871055</v>
+        <v>29.84613337694412</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>292.290489255438</v>
+        <v>-191.5084691463495</v>
       </c>
     </row>
     <row r="31">
@@ -1040,10 +1040,10 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>23.43257559588321</v>
+        <v>-23.43257559588321</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>241.8994792008937</v>
+        <v>-241.8994792008937</v>
       </c>
     </row>
     <row r="33">
@@ -7416,10 +7416,10 @@
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.084537</v>
+        <v>-0.084537</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>1.177915</v>
+        <v>-1.177915</v>
       </c>
     </row>
     <row r="120">

--- a/output/pdf_financials_xlsx/CCDS.xlsx
+++ b/output/pdf_financials_xlsx/CCDS.xlsx
@@ -1083,16 +1083,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.979428</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.030805</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.025635</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.967292</v>
       </c>
     </row>
     <row r="35">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.979428</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.030805</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.025635</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.967292</v>
       </c>
     </row>
     <row r="37">
@@ -1349,16 +1349,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.048261</v>
+        <v>0.06883300000000001</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.025835</v>
+        <v>0.0002</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.402544</v>
+        <v>0.435252</v>
       </c>
     </row>
     <row r="49">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">

--- a/output/pdf_financials_xlsx/CCDS.xlsx
+++ b/output/pdf_financials_xlsx/CCDS.xlsx
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004502</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.028405</v>
+        <v>-0.08326699999999999</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.010744</v>
@@ -2938,10 +2938,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
@@ -2999,10 +2997,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.979428</v>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
@@ -3065,7 +3061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H142"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6266,7 +6262,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="n">
         <v>1.3425</v>
       </c>
@@ -6649,58 +6649,62 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Colocation 12 $</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>-0.004502</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G99" s="5" t="n">
-        <v>0.360767</v>
-      </c>
-      <c r="H99" s="5" t="n">
-        <v>0.397424</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sale of equipment</t>
+          <t>Deferred financing costs</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E100" s="5" t="n">
+        <v>-0.050683</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -6712,103 +6716,111 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H100" s="5" t="n">
-        <v>0.08952</v>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Total revenue</t>
+          <t>Changes in non-cash working capital total</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>-0.08326699999999999</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G101" s="5" t="n">
-        <v>0.360767</v>
-      </c>
-      <c r="H101" s="5" t="n">
-        <v>0.486944</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cost of revenue</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Data center operating costs</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Financing activities total</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>1.062695</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G102" s="5" t="n">
-        <v>0.180314</v>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>0.196662</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cost of revenue</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cost of equipment</t>
+          <t>Net cash inflow</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E103" s="5" t="n">
+        <v>0.979428</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -6820,29 +6832,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H103" s="5" t="n">
-        <v>0.06275</v>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cost of revenue</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Total cost of revenue</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6855,49 +6869,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G104" s="5" t="n">
-        <v>0.180314</v>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>0.259412</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cost of revenue</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Cash, end of period $</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>0.979428</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G105" s="5" t="n">
-        <v>0.180453</v>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>0.227532</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -6908,19 +6928,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Advertising and promotion</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Colocation 12 $</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -6931,13 +6947,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G106" s="5" t="n">
+        <v>0.360767</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>0.012845</v>
+        <v>0.397424</v>
       </c>
     </row>
     <row r="107">
@@ -6948,19 +6962,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 6, 7</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Sale of equipment</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -6971,11 +6981,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G107" s="5" t="n">
-        <v>0.192212</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>0.245376</v>
+        <v>0.08952</v>
       </c>
     </row>
     <row r="108">
@@ -6986,17 +6998,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Total revenue</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7010,10 +7022,10 @@
         </is>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.008643</v>
+        <v>0.360767</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>0.022182</v>
+        <v>0.486944</v>
       </c>
     </row>
     <row r="109">
@@ -7024,19 +7036,15 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Cost of revenue</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Filing fee</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Data center operating costs</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -7047,13 +7055,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G109" s="5" t="n">
+        <v>0.180314</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>0.027608</v>
+        <v>0.196662</v>
       </c>
     </row>
     <row r="110">
@@ -7064,19 +7070,15 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Cost of revenue</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Management fee 9</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Cost of equipment</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -7093,7 +7095,7 @@
         </is>
       </c>
       <c r="H110" s="5" t="n">
-        <v>0.165</v>
+        <v>0.06275</v>
       </c>
     </row>
     <row r="111">
@@ -7104,15 +7106,19 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Cost of revenue</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Stock based compensation 9, 10</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>Total cost of revenue</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -7123,13 +7129,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G111" s="5" t="n">
+        <v>0.180314</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>0.2696</v>
+        <v>0.259412</v>
       </c>
     </row>
     <row r="112">
@@ -7140,15 +7144,19 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Cost of revenue</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Receivable written off</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -7159,13 +7167,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G112" s="5" t="n">
+        <v>0.180453</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>0.008541999999999999</v>
+        <v>0.227532</v>
       </c>
     </row>
     <row r="113">
@@ -7181,12 +7187,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Advertising and promotion</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7199,11 +7205,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G113" s="5" t="n">
-        <v>0.039984</v>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H113" s="5" t="n">
-        <v>0.123366</v>
+        <v>0.012845</v>
       </c>
     </row>
     <row r="114">
@@ -7219,10 +7227,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Total expenses before the undernoted</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>Depreciation and amortization 6, 7</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -7234,10 +7246,10 @@
         </is>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.240839</v>
+        <v>0.192212</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>0.874519</v>
+        <v>0.245376</v>
       </c>
     </row>
     <row r="115">
@@ -7248,17 +7260,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7272,10 +7284,10 @@
         </is>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.024151</v>
+        <v>0.008643</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>0.045108</v>
+        <v>0.022182</v>
       </c>
     </row>
     <row r="116">
@@ -7286,15 +7298,19 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Listing expense 4</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>Filing fee</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -7311,7 +7327,7 @@
         </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>0.54582</v>
+        <v>0.027608</v>
       </c>
     </row>
     <row r="117">
@@ -7322,15 +7338,19 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Unrealized gain on investment 5</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>Management fee 9</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -7347,7 +7367,7 @@
         </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>-0.06</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="118">
@@ -7358,12 +7378,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Total other expenses</t>
+          <t>Stock based compensation 9, 10</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -7377,11 +7397,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G118" s="5" t="n">
-        <v>0.024151</v>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H118" s="5" t="n">
-        <v>0.530928</v>
+        <v>0.2696</v>
       </c>
     </row>
     <row r="119">
@@ -7392,19 +7414,15 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Receivable written off</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -7415,11 +7433,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G119" s="5" t="n">
-        <v>-0.084537</v>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H119" s="5" t="n">
-        <v>-1.177915</v>
+        <v>0.008541999999999999</v>
       </c>
     </row>
     <row r="120">
@@ -7430,15 +7450,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>6,353,982               2,751,470shares, basic and diluted</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Balance at June 30, 2023 2,751,470 $ 600 - $</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -7450,10 +7474,10 @@
         </is>
       </c>
       <c r="G120" s="5" t="n">
-        <v>-0.221596</v>
+        <v>0.039984</v>
       </c>
       <c r="H120" s="5" t="n">
-        <v>-0.222196</v>
+        <v>0.123366</v>
       </c>
     </row>
     <row r="121">
@@ -7464,19 +7488,15 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>6,353,982               2,751,470shares, basic and diluted</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Total expenses before the undernoted</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -7488,10 +7508,10 @@
         </is>
       </c>
       <c r="G121" s="5" t="n">
-        <v>-0.084537</v>
+        <v>0.240839</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>-0.084537</v>
+        <v>0.874519</v>
       </c>
     </row>
     <row r="122">
@@ -7502,15 +7522,19 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>6,353,982               2,751,470shares, basic and diluted</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Balance as at June 30, 2024 2,751,470 $ 600 - $</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -7522,10 +7546,10 @@
         </is>
       </c>
       <c r="G122" s="5" t="n">
-        <v>-0.306133</v>
+        <v>0.024151</v>
       </c>
       <c r="H122" s="5" t="n">
-        <v>-0.306733</v>
+        <v>0.045108</v>
       </c>
     </row>
     <row r="123">
@@ -7536,12 +7560,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6,353,982               2,751,470shares, basic and diluted</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Shares issued as part of the debt settlement 10 848,530 339,874 -</t>
+          <t>Listing expense 4</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -7555,13 +7579,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G123" s="5" t="n">
-        <v>0.339874</v>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>0.54582</v>
       </c>
     </row>
     <row r="124">
@@ -7572,12 +7596,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>6,353,982               2,751,470shares, basic and diluted</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Shares issued to former Hopefield Ventures 4 5,999,998 900,000 -</t>
+          <t>Unrealized gain on investment 5</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -7591,13 +7615,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G124" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="125">
@@ -7608,12 +7632,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Two Inc. shareholders on reverse takeover</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Shares issued in March 2025 private 10 1,669,000 244,592 -</t>
+          <t>Total other expenses</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -7628,12 +7652,10 @@
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.244592</v>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.024151</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>0.530928</v>
       </c>
     </row>
     <row r="126">
@@ -7644,15 +7666,19 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>placement, net of share issue costs</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Shares issued in May 2025 private 10 2,000,000 937,715 5,404</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -7664,12 +7690,10 @@
         </is>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.943119</v>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.084537</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>-1.177915</v>
       </c>
     </row>
     <row r="127">
@@ -7680,12 +7704,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>placement, net of share issue costs</t>
+          <t>6,353,982               2,751,470shares, basic and diluted</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Exercise of warrants 10 21,014 6,336 (44)</t>
+          <t>Balance at June 30, 2023 2,751,470 $ 600 - $</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -7700,12 +7724,10 @@
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.006292</v>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.221596</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>-0.222196</v>
       </c>
     </row>
     <row r="128">
@@ -7716,15 +7738,19 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>placement, net of share issue costs</t>
+          <t>6,353,982               2,751,470shares, basic and diluted</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Stock options granted on reverse takeover 4 - - 68,670</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -7736,12 +7762,10 @@
         </is>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.06866999999999999</v>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.084537</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>-0.084537</v>
       </c>
     </row>
     <row r="129">
@@ -7752,12 +7776,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>placement, net of share issue costs</t>
+          <t>6,353,982               2,751,470shares, basic and diluted</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Stock options granted 10 - - 269,600</t>
+          <t>Balance as at June 30, 2024 2,751,470 $ 600 - $</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -7772,12 +7796,10 @@
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.2696</v>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.306133</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>-0.306733</v>
       </c>
     </row>
     <row r="130">
@@ -7788,12 +7810,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>placement, net of share issue costs</t>
+          <t>6,353,982               2,751,470shares, basic and diluted</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Investment contribution 5</t>
+          <t>Shares issued as part of the debt settlement 10 848,530 339,874 -</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -7808,10 +7830,12 @@
         </is>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H130" s="5" t="n">
-        <v>0.24</v>
+        <v>0.339874</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -7822,19 +7846,15 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>placement, net of share issue costs</t>
+          <t>6,353,982               2,751,470shares, basic and diluted</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Shares issued to former Hopefield Ventures 4 5,999,998 900,000 -</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -7846,10 +7866,12 @@
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>-1.177915</v>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>-1.177915</v>
+        <v>0.9</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -7860,12 +7882,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>placement, net of share issue costs</t>
+          <t>Two Inc. shareholders on reverse takeover</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Balance as at June 30, 2025 13,290,012 2,429,117 583,630 $</t>
+          <t>Shares issued in March 2025 private 10 1,669,000 244,592 -</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -7880,10 +7902,12 @@
         </is>
       </c>
       <c r="G132" s="5" t="n">
-        <v>1.528099</v>
-      </c>
-      <c r="H132" s="5" t="n">
-        <v>-1.484648</v>
+        <v>0.244592</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -7894,25 +7918,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Period from</t>
+          <t>placement, net of share issue costs</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2023 December</t>
+          <t>Shares issued in May 2025 private 10 2,000,000 937,715 5,404</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
-      <c r="E133" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="F133" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>0.943119</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -7928,29 +7954,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>placement, net of share issue costs</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Filing fees $</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="n">
-        <v>0.014124</v>
-      </c>
-      <c r="F134" s="5" t="n">
-        <v>0.021516</v>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exercise of warrants 10 21,014 6,336 (44)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0.006292</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -7966,29 +7990,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>placement, net of share issue costs</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Office and administration</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="n">
-        <v>0.001383</v>
-      </c>
-      <c r="F135" s="5" t="n">
-        <v>0.000526</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Stock options granted on reverse takeover 4 - - 68,670</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.06866999999999999</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -8004,29 +8026,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>placement, net of share issue costs</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="n">
-        <v>0.039927</v>
-      </c>
-      <c r="F136" s="5" t="n">
-        <v>0.095002</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Stock options granted 10 - - 269,600</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.2696</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -8042,32 +8062,30 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>placement, net of share issue costs</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Promotion</t>
+          <t>Investment contribution 5</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
-      <c r="E137" s="5" t="n">
-        <v>0.001053</v>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G137" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="138">
@@ -8078,17 +8096,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>placement, net of share issue costs</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
+          <t>Net loss for the year - - -</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8096,18 +8114,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F138" s="5" t="n">
-        <v>0.011116</v>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>-1.177915</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>-1.177915</v>
       </c>
     </row>
     <row r="139">
@@ -8118,30 +8134,30 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>placement, net of share issue costs</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 5 &amp; 6)</t>
+          <t>Balance as at June 30, 2025 13,290,012 2,429,117 583,630 $</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" s="5" t="n">
-        <v>0.084995</v>
-      </c>
-      <c r="F139" s="5" t="n">
-        <v>0.01475</v>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>1.528099</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>-1.484648</v>
       </c>
     </row>
     <row r="140">
@@ -8152,24 +8168,20 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Period from</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>2023 December</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" s="5" t="n">
-        <v>-0.141482</v>
+        <v>0.002022</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>-0.14291</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -8195,19 +8207,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Filing fees $</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.014124</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.021516</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -8233,26 +8245,484 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
+          <t>Office and administration</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>0.001383</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>0.000526</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>0.039927</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>0.095002</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Promotion</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" s="5" t="n">
+        <v>0.001053</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>0.011116</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Notes 5 &amp; 6)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" s="5" t="n">
+        <v>0.084995</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>0.01475</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>-0.141482</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>-0.14291</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
           <t>Weighted average number of shares outstanding (Note 5)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>BasicAverageShares</t>
         </is>
       </c>
-      <c r="E142" s="5" t="n">
+      <c r="E149" s="5" t="n">
         <v>16.093146</v>
       </c>
-      <c r="F142" s="5" t="n">
+      <c r="F149" s="5" t="n">
         <v>8.432705</v>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Professional fees $</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="n">
+        <v>0.039927</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Filing fees</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="n">
+        <v>0.014124</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 4)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" s="5" t="n">
+        <v>0.084995</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="n">
+        <v>-0.141482</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="n">
+        <v>16.093146</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
         <is>
           <t>-</t>
         </is>
